--- a/artfynd/A 37766-2026 artfynd.xlsx
+++ b/artfynd/A 37766-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137438245</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137438251</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137438252</v>
       </c>
       <c r="B4" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,32 +1016,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137438244</v>
+        <v>137438505</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>91186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621197</v>
+        <v>621194</v>
       </c>
       <c r="R5" t="n">
-        <v>6635007</v>
+        <v>6635126</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,38 +1122,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438244</t>
+          <t>https://artportalen.se/Sighting/137438505</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137438255</v>
+        <v>137438244</v>
       </c>
       <c r="B6" t="n">
-        <v>93519</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621120</v>
+        <v>621197</v>
       </c>
       <c r="R6" t="n">
-        <v>6635180</v>
+        <v>6635007</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438255</t>
+          <t>https://artportalen.se/Sighting/137438244</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137438258</v>
+        <v>137438255</v>
       </c>
       <c r="B7" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621147</v>
+        <v>621120</v>
       </c>
       <c r="R7" t="n">
-        <v>6635164</v>
+        <v>6635180</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1346,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438258</t>
+          <t>https://artportalen.se/Sighting/137438255</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137438261</v>
+        <v>137438258</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621154</v>
+        <v>621147</v>
       </c>
       <c r="R8" t="n">
-        <v>6635042</v>
+        <v>6635164</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1458,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438261</t>
+          <t>https://artportalen.se/Sighting/137438258</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137438262</v>
+        <v>137438261</v>
       </c>
       <c r="B9" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621173</v>
+        <v>621154</v>
       </c>
       <c r="R9" t="n">
-        <v>6634997</v>
+        <v>6635042</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,52 +1570,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438262</t>
+          <t>https://artportalen.se/Sighting/137438261</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137438249</v>
+        <v>137438262</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>93520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621146</v>
+        <v>621173</v>
       </c>
       <c r="R10" t="n">
-        <v>6635074</v>
+        <v>6634997</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1647,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,13 +1682,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438249</t>
+          <t>https://artportalen.se/Sighting/137438262</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137438259</v>
+        <v>137438249</v>
       </c>
       <c r="B11" t="n">
         <v>58032</v>
@@ -1725,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621148</v>
+        <v>621146</v>
       </c>
       <c r="R11" t="n">
-        <v>6635165</v>
+        <v>6635074</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1770,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,16 +1795,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438259</t>
+          <t>https://artportalen.se/Sighting/137438249</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137438238</v>
+        <v>137438259</v>
       </c>
       <c r="B12" t="n">
-        <v>5188</v>
+        <v>58032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,34 +1812,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621134</v>
+        <v>621148</v>
       </c>
       <c r="R12" t="n">
-        <v>6634941</v>
+        <v>6635165</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,13 +1908,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438238</t>
+          <t>https://artportalen.se/Sighting/137438259</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137438239</v>
+        <v>137438238</v>
       </c>
       <c r="B13" t="n">
         <v>5188</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621139</v>
+        <v>621134</v>
       </c>
       <c r="R13" t="n">
-        <v>6634937</v>
+        <v>6634941</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,16 +2020,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438239</t>
+          <t>https://artportalen.se/Sighting/137438238</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137438254</v>
+        <v>137438239</v>
       </c>
       <c r="B14" t="n">
-        <v>4789</v>
+        <v>5188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621131</v>
+        <v>621139</v>
       </c>
       <c r="R14" t="n">
-        <v>6635203</v>
+        <v>6634937</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,13 +2132,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438254</t>
+          <t>https://artportalen.se/Sighting/137438239</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137438257</v>
+        <v>137438254</v>
       </c>
       <c r="B15" t="n">
         <v>4789</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621129</v>
+        <v>621131</v>
       </c>
       <c r="R15" t="n">
-        <v>6635171</v>
+        <v>6635203</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,56 +2244,51 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438257</t>
+          <t>https://artportalen.se/Sighting/137438254</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137438246</v>
+        <v>137438257</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>4789</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621215</v>
+        <v>621129</v>
       </c>
       <c r="R16" t="n">
-        <v>6635010</v>
+        <v>6635171</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,41 +2356,46 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438246</t>
+          <t>https://artportalen.se/Sighting/137438257</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137438247</v>
+        <v>137438246</v>
       </c>
       <c r="B17" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,16 +2473,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438247</t>
+          <t>https://artportalen.se/Sighting/137438246</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137438256</v>
+        <v>137438247</v>
       </c>
       <c r="B18" t="n">
-        <v>5208</v>
+        <v>58191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621130</v>
+        <v>621215</v>
       </c>
       <c r="R18" t="n">
-        <v>6635171</v>
+        <v>6635010</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,13 +2585,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438256</t>
+          <t>https://artportalen.se/Sighting/137438247</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137438260</v>
+        <v>137438256</v>
       </c>
       <c r="B19" t="n">
         <v>5208</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621155</v>
+        <v>621130</v>
       </c>
       <c r="R19" t="n">
-        <v>6635147</v>
+        <v>6635171</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,16 +2697,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438260</t>
+          <t>https://artportalen.se/Sighting/137438256</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137438250</v>
+        <v>137438260</v>
       </c>
       <c r="B20" t="n">
-        <v>8470</v>
+        <v>5208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621145</v>
+        <v>621155</v>
       </c>
       <c r="R20" t="n">
-        <v>6635077</v>
+        <v>6635147</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,60 +2809,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438250</t>
+          <t>https://artportalen.se/Sighting/137438260</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137438265</v>
+        <v>137438250</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>8470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621195</v>
+        <v>621145</v>
       </c>
       <c r="R21" t="n">
-        <v>6634970</v>
+        <v>6635077</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2894,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2904,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,16 +2921,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438265</t>
+          <t>https://artportalen.se/Sighting/137438250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137438266</v>
+        <v>137438265</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2957,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2980,10 +2971,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621207</v>
+        <v>621195</v>
       </c>
       <c r="R22" t="n">
-        <v>6634972</v>
+        <v>6634970</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3015,7 +3006,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3016,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,16 +3042,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438266</t>
+          <t>https://artportalen.se/Sighting/137438265</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137438267</v>
+        <v>137438266</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3078,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3101,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621216</v>
+        <v>621207</v>
       </c>
       <c r="R23" t="n">
-        <v>6634976</v>
+        <v>6634972</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3136,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,51 +3163,60 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137438267</t>
+          <t>https://artportalen.se/Sighting/137438266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137438240</v>
+        <v>137438267</v>
       </c>
       <c r="B24" t="n">
-        <v>98295</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bredmossen S, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621143</v>
+        <v>621216</v>
       </c>
       <c r="R24" t="n">
-        <v>6634935</v>
+        <v>6634976</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,6 +3283,118 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137438267</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137438240</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98296</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bredmossen S, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>621143</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634935</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137438240</t>
         </is>
@@ -3313,6 +3425,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37766-2026 artfynd.xlsx
+++ b/artfynd/A 37766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438245</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137438251</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137438252</v>
       </c>
       <c r="B4" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137438505</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137438244</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137438255</v>
       </c>
       <c r="B7" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137438258</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137438261</v>
       </c>
       <c r="B9" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137438262</v>
       </c>
       <c r="B10" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137438265</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>137438266</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>137438267</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>137438240</v>
       </c>
       <c r="B25" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37766-2026 artfynd.xlsx
+++ b/artfynd/A 37766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137438245</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137438251</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137438252</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137438505</v>
       </c>
       <c r="B5" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137438244</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137438255</v>
       </c>
       <c r="B7" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137438258</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137438261</v>
       </c>
       <c r="B9" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137438262</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137438249</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137438259</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137438246</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>137438247</v>
       </c>
       <c r="B18" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137438265</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>137438266</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>137438267</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>137438240</v>
       </c>
       <c r="B25" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
